--- a/files/Data Cleaning Excel Tutorial.xlsx
+++ b/files/Data Cleaning Excel Tutorial.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\advance_excel\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2BD89D7-2E52-496B-A45A-61E371100455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A75A958-64F6-450D-85C5-B7770C3065CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
     <sheet name="US_Presidents Excel Tutorial Da" sheetId="1" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'US_Presidents Excel Tutorial Da'!$A$1:$L$48</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId3"/>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="143">
   <si>
     <t>S.No.</t>
   </si>
@@ -80,18 +83,12 @@
     <t>Democratic-  Republican</t>
   </si>
   <si>
-    <t xml:space="preserve">    Aaron Burr</t>
-  </si>
-  <si>
     <t>James Madison</t>
   </si>
   <si>
     <t>5th  United States Secretary of State   (1801â€“1809)</t>
   </si>
   <si>
-    <t>George    Clinton</t>
-  </si>
-  <si>
     <t>JAMES MONROE</t>
   </si>
   <si>
@@ -119,9 +116,6 @@
     <t>Democratic</t>
   </si>
   <si>
-    <t>John C.     Calhoun</t>
-  </si>
-  <si>
     <t>Martin Van Buren</t>
   </si>
   <si>
@@ -161,18 +155,12 @@
     <t>9th  Governor of Tennessee   (1839â€“1841)</t>
   </si>
   <si>
-    <t>George         M. Dallas</t>
-  </si>
-  <si>
     <t>Zachary Taylor</t>
   </si>
   <si>
     <t>Major General  of the  1st Infantry Regiment   United States Army   (1846â€“1849)</t>
   </si>
   <si>
-    <t xml:space="preserve">               Millard Fillmore</t>
-  </si>
-  <si>
     <t>Millard Fillmore</t>
   </si>
   <si>
@@ -459,16 +447,36 @@
   </si>
   <si>
     <t>REVENUE</t>
+  </si>
+  <si>
+    <t>president_fixed</t>
+  </si>
+  <si>
+    <t>date_text</t>
+  </si>
+  <si>
+    <t>date_fix</t>
+  </si>
+  <si>
+    <t>vice-fixed</t>
+  </si>
+  <si>
+    <t>Aaron Burr</t>
+  </si>
+  <si>
+    <t>George Clinton</t>
+  </si>
+  <si>
+    <t>George M. Dallas</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+  <numFmts count="2">
+    <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -953,18 +961,16 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1010,39 +1016,39 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="46">
+  <dxfs count="18">
     <dxf>
-      <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
+      <numFmt numFmtId="167" formatCode="&quot;₹&quot;\ #,##0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
+      <numFmt numFmtId="167" formatCode="&quot;₹&quot;\ #,##0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
     </dxf>
     <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
+      <numFmt numFmtId="167" formatCode="&quot;₹&quot;\ #,##0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
+      <numFmt numFmtId="167" formatCode="&quot;₹&quot;\ #,##0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
     </dxf>
     <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
@@ -1051,103 +1057,19 @@
       <numFmt numFmtId="14" formatCode="0.00%"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
+      <numFmt numFmtId="167" formatCode="&quot;₹&quot;\ #,##0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+      <numFmt numFmtId="167" formatCode="&quot;₹&quot;\ #,##0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1165,7 +1087,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="HETVI" refreshedDate="46115.474507638886" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{84DB722D-7587-4CE2-BDBE-E9B77BE2C401}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:H1048576" sheet="US_Presidents Excel Tutorial Da"/>
+    <worksheetSource ref="A1:K1048576" sheet="US_Presidents Excel Tutorial Da"/>
   </cacheSource>
   <cacheFields count="8">
     <cacheField name="S.No." numFmtId="0">
@@ -1874,19 +1796,19 @@
     <dataField name="REVENUE" fld="5" showDataAs="percentOfTotal" baseField="3" baseItem="0" numFmtId="10"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="42">
+    <format dxfId="17">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="41">
+    <format dxfId="16">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="40">
+    <format dxfId="15">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="39">
+    <format dxfId="14">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="38">
+    <format dxfId="13">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
     <format dxfId="12">
@@ -2208,106 +2130,106 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9866A72B-CDF8-4754-B73E-1F6E9A8EC660}">
-  <dimension ref="A3:B29"/>
+  <dimension ref="A3:B32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="41.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>140</v>
+      <c r="A3" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B4" s="8">
+      <c r="A4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="5">
         <v>0.47481181239143022</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="8">
+      <c r="A5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="5">
         <v>0.41459177764910249</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B6" s="8">
+      <c r="A6" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" s="5">
         <v>4.6902142443543716E-2</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B7" s="5">
+        <v>2.605674580196873E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="5">
+        <v>1.9687319050376375E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="5">
+        <v>1.0422698320787493E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="5">
+        <v>5.7903879559930514E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5">
+        <v>1.1580775911986102E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B12" s="5">
+        <v>5.7903879559930511E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B7" s="8">
-        <v>2.605674580196873E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="8">
-        <v>1.9687319050376375E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="8">
-        <v>1.0422698320787493E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="8">
-        <v>5.7903879559930514E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="8">
-        <v>1.1580775911986102E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B12" s="8">
-        <v>5.7903879559930511E-4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="B13" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="B14" s="8">
+      <c r="B14" s="5">
         <v>1</v>
       </c>
     </row>
@@ -2355,6 +2277,15 @@
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B29"/>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B30"/>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B31"/>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B32"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2363,13 +2294,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr defaultColWidth="23.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="6" width="23.5546875" style="3"/>
+    <col min="9" max="9" width="23.5546875" style="6"/>
+    <col min="10" max="11" width="23.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2377,1247 +2309,2172 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="G1" t="s">
-        <v>136</v>
-      </c>
-      <c r="H1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I1" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="L1" t="s">
+        <v>137</v>
+      </c>
+      <c r="M1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="str">
+        <f>UPPER(B2)</f>
+        <v>GEORGE WASHINGTON</v>
+      </c>
+      <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
-        <v>131</v>
-      </c>
       <c r="E2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F2" t="str">
+        <f>TRIM(G2)</f>
+        <v>John Adams</v>
+      </c>
+      <c r="G2" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="4">
+      <c r="H2" t="str">
+        <f>TRIM(G2)</f>
+        <v>John Adams</v>
+      </c>
+      <c r="I2" s="6">
         <v>5000</v>
       </c>
-      <c r="G2" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H2" s="1">
+      <c r="J2" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K2" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L2" t="str">
+        <f>TEXT(J2,"dd-mm-yyyy")</f>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M2" t="str">
+        <f>SUBSTITUTE(L2,"-","/")</f>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" t="str">
+        <f t="shared" ref="C3:C47" si="0">UPPER(B3)</f>
+        <v>JOHN ADAMS</v>
+      </c>
+      <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="str">
+        <f t="shared" ref="F3:F48" si="1">TRIM(G3)</f>
+        <v>Thomas Jefferson</v>
+      </c>
+      <c r="G3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="4">
+      <c r="H3" t="str">
+        <f t="shared" ref="H3:H48" si="2">TRIM(G3)</f>
+        <v>Thomas Jefferson</v>
+      </c>
+      <c r="I3" s="6">
         <v>10000</v>
       </c>
-      <c r="G3" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H3" s="1">
+      <c r="J3" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K3" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L3" t="str">
+        <f t="shared" ref="L3:L48" si="3">TEXT(J3,"dd-mm-yyyy")</f>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M3" t="str">
+        <f t="shared" ref="M3:M48" si="4">SUBSTITUTE(L3,"-","/")</f>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" t="str">
+        <f t="shared" si="0"/>
+        <v>THOMAS JEFFERSON</v>
+      </c>
+      <c r="D4" t="s">
         <v>12</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="4">
+      <c r="F4" t="str">
+        <f t="shared" si="1"/>
+        <v>Aaron Burr</v>
+      </c>
+      <c r="G4" t="s">
+        <v>140</v>
+      </c>
+      <c r="H4" t="str">
+        <f t="shared" si="2"/>
+        <v>Aaron Burr</v>
+      </c>
+      <c r="I4" s="6">
         <v>15000</v>
       </c>
-      <c r="G4" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H4" s="1">
+      <c r="J4" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K4" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L4" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M4" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="str">
+        <f t="shared" si="0"/>
+        <v>JAMES MADISON</v>
+      </c>
+      <c r="D5" t="s">
         <v>15</v>
       </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>13</v>
       </c>
-      <c r="E5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="4">
+      <c r="F5" t="str">
+        <f t="shared" si="1"/>
+        <v>George Clinton</v>
+      </c>
+      <c r="G5" t="s">
+        <v>141</v>
+      </c>
+      <c r="H5" t="str">
+        <f t="shared" si="2"/>
+        <v>George Clinton</v>
+      </c>
+      <c r="I5" s="6">
         <v>20000</v>
       </c>
-      <c r="G5" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H5" s="1">
+      <c r="J5" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K5" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L5" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M5" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="str">
+        <f t="shared" si="0"/>
+        <v>JAMES MONROE</v>
+      </c>
+      <c r="D6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="str">
+        <f t="shared" si="1"/>
+        <v>Daniel D. Tompkins</v>
+      </c>
+      <c r="G6" t="s">
         <v>18</v>
       </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="4">
+      <c r="H6" t="str">
+        <f t="shared" si="2"/>
+        <v>Daniel D. Tompkins</v>
+      </c>
+      <c r="I6" s="6">
         <v>25000</v>
       </c>
-      <c r="G6" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H6" s="1">
+      <c r="J6" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K6" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L6" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M6" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="str">
+        <f t="shared" si="0"/>
+        <v>JOHN QUINCY ADAMS</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="str">
+        <f t="shared" si="1"/>
+        <v>John C. Calhoun</v>
+      </c>
+      <c r="G7" t="s">
         <v>21</v>
       </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="4">
+      <c r="H7" t="str">
+        <f t="shared" si="2"/>
+        <v>John C. Calhoun</v>
+      </c>
+      <c r="I7" s="6">
         <v>30000</v>
       </c>
-      <c r="G7" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H7" s="1">
+      <c r="J7" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K7" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L7" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M7" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="str">
+        <f t="shared" si="0"/>
+        <v>ANDREW JACKSON</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
         <v>24</v>
       </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="4">
+      <c r="F8" t="str">
+        <f t="shared" si="1"/>
+        <v>John C. Calhoun</v>
+      </c>
+      <c r="G8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" t="str">
+        <f t="shared" si="2"/>
+        <v>John C. Calhoun</v>
+      </c>
+      <c r="I8" s="6">
         <v>35000</v>
       </c>
-      <c r="G8" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H8" s="1">
+      <c r="J8" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K8" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L8" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M8" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>29</v>
+        <v>25</v>
+      </c>
+      <c r="C9" t="str">
+        <f t="shared" si="0"/>
+        <v>MARTIN VAN BUREN</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="4">
+        <v>24</v>
+      </c>
+      <c r="F9" t="str">
+        <f t="shared" si="1"/>
+        <v>Richard Mentor Johnson</v>
+      </c>
+      <c r="G9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" t="str">
+        <f t="shared" si="2"/>
+        <v>Richard Mentor Johnson</v>
+      </c>
+      <c r="I9" s="6">
         <v>40000</v>
       </c>
-      <c r="G9" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H9" s="1">
+      <c r="J9" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K9" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L9" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M9" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="str">
+        <f t="shared" si="0"/>
+        <v>WILLIAM HENRY HARRISON</v>
+      </c>
+      <c r="D10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" t="str">
+        <f t="shared" si="1"/>
+        <v>John Tyler</v>
+      </c>
+      <c r="G10" t="s">
         <v>31</v>
       </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="4">
+      <c r="H10" t="str">
+        <f t="shared" si="2"/>
+        <v>John Tyler</v>
+      </c>
+      <c r="I10" s="6">
         <v>45000</v>
       </c>
-      <c r="G10" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H10" s="1">
+      <c r="J10" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K10" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L10" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M10" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="str">
+        <f t="shared" si="0"/>
+        <v>JOHN TYLER</v>
+      </c>
+      <c r="D11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" t="str">
+        <f t="shared" si="1"/>
+        <v>Office vacant</v>
+      </c>
+      <c r="G11" t="s">
         <v>35</v>
       </c>
-      <c r="C11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" s="4">
+      <c r="H11" t="str">
+        <f t="shared" si="2"/>
+        <v>Office vacant</v>
+      </c>
+      <c r="I11" s="6">
         <v>50000</v>
       </c>
-      <c r="G11" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H11" s="1">
+      <c r="J11" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K11" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L11" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M11" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" t="s">
-        <v>40</v>
+        <v>36</v>
+      </c>
+      <c r="C12" t="str">
+        <f t="shared" si="0"/>
+        <v>JAMES K. POLK</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="E12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F12" s="4">
+        <v>24</v>
+      </c>
+      <c r="F12" t="str">
+        <f t="shared" si="1"/>
+        <v>George M. Dallas</v>
+      </c>
+      <c r="G12" t="s">
+        <v>142</v>
+      </c>
+      <c r="H12" t="str">
+        <f t="shared" si="2"/>
+        <v>George M. Dallas</v>
+      </c>
+      <c r="I12" s="6">
         <v>55000</v>
       </c>
-      <c r="G12" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H12" s="1">
+      <c r="J12" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K12" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L12" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M12" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" t="s">
-        <v>43</v>
+        <v>38</v>
+      </c>
+      <c r="C13" t="str">
+        <f t="shared" si="0"/>
+        <v>ZACHARY TAYLOR</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E13" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13" s="4">
+        <v>30</v>
+      </c>
+      <c r="F13" t="str">
+        <f t="shared" si="1"/>
+        <v>Millard Fillmore</v>
+      </c>
+      <c r="G13" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13" t="str">
+        <f t="shared" si="2"/>
+        <v>Millard Fillmore</v>
+      </c>
+      <c r="I13" s="6">
         <v>60000</v>
       </c>
-      <c r="G13" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H13" s="1">
+      <c r="J13" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K13" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L13" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M13" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" t="s">
-        <v>46</v>
+        <v>40</v>
+      </c>
+      <c r="C14" t="str">
+        <f t="shared" si="0"/>
+        <v>MILLARD FILLMORE</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E14" t="s">
-        <v>38</v>
-      </c>
-      <c r="F14" s="4">
+        <v>30</v>
+      </c>
+      <c r="F14" t="str">
+        <f t="shared" si="1"/>
+        <v>Office vacant</v>
+      </c>
+      <c r="G14" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" t="str">
+        <f t="shared" si="2"/>
+        <v>Office vacant</v>
+      </c>
+      <c r="I14" s="6">
         <v>65000</v>
       </c>
-      <c r="G14" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H14" s="1">
+      <c r="J14" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K14" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L14" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M14" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="C15" t="str">
+        <f t="shared" si="0"/>
+        <v>FRANKLIN PIERCE</v>
       </c>
       <c r="D15" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E15" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" s="4">
+        <v>24</v>
+      </c>
+      <c r="F15" t="str">
+        <f t="shared" si="1"/>
+        <v>William R. King</v>
+      </c>
+      <c r="G15" t="s">
+        <v>44</v>
+      </c>
+      <c r="H15" t="str">
+        <f t="shared" si="2"/>
+        <v>William R. King</v>
+      </c>
+      <c r="I15" s="6">
         <v>75000</v>
       </c>
-      <c r="G15" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H15" s="1">
+      <c r="J15" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K15" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L15" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M15" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" t="s">
-        <v>51</v>
+        <v>45</v>
+      </c>
+      <c r="C16" t="str">
+        <f t="shared" si="0"/>
+        <v>JAMES BUCHANAN</v>
       </c>
       <c r="D16" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="E16" t="s">
-        <v>52</v>
-      </c>
-      <c r="F16" s="4">
+        <v>24</v>
+      </c>
+      <c r="F16" t="str">
+        <f t="shared" si="1"/>
+        <v>John C. Breckinridge</v>
+      </c>
+      <c r="G16" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" t="str">
+        <f t="shared" si="2"/>
+        <v>John C. Breckinridge</v>
+      </c>
+      <c r="I16" s="6">
         <v>85000</v>
       </c>
-      <c r="G16" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H16" s="1">
+      <c r="J16" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K16" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L16" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M16" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C17" t="s">
-        <v>54</v>
+        <v>48</v>
+      </c>
+      <c r="C17" t="str">
+        <f t="shared" si="0"/>
+        <v>ABRAHAM LINCOLN</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E17" t="s">
         <v>55</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" t="str">
+        <f t="shared" si="1"/>
+        <v>Hannibal Hamlin</v>
+      </c>
+      <c r="G17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H17" t="str">
+        <f t="shared" si="2"/>
+        <v>Hannibal Hamlin</v>
+      </c>
+      <c r="I17" s="6">
         <v>95000</v>
       </c>
-      <c r="G17" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H17" s="1">
+      <c r="J17" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K17" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L17" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M17" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18" t="s">
-        <v>57</v>
+        <v>51</v>
+      </c>
+      <c r="C18" t="str">
+        <f t="shared" si="0"/>
+        <v>ANDREW JOHNSON</v>
       </c>
       <c r="D18" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="E18" t="s">
-        <v>38</v>
-      </c>
-      <c r="F18" s="4">
+        <v>24</v>
+      </c>
+      <c r="F18" t="str">
+        <f t="shared" si="1"/>
+        <v>Office vacant</v>
+      </c>
+      <c r="G18" t="s">
+        <v>35</v>
+      </c>
+      <c r="H18" t="str">
+        <f t="shared" si="2"/>
+        <v>Office vacant</v>
+      </c>
+      <c r="I18" s="6">
         <v>105000</v>
       </c>
-      <c r="G18" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H18" s="1">
+      <c r="J18" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K18" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L18" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M18" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" t="s">
-        <v>59</v>
+        <v>53</v>
+      </c>
+      <c r="C19" t="str">
+        <f t="shared" si="0"/>
+        <v>ULYSSES S. GRANT</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E19" t="s">
-        <v>61</v>
-      </c>
-      <c r="F19" s="4">
+        <v>55</v>
+      </c>
+      <c r="F19" t="str">
+        <f t="shared" si="1"/>
+        <v>Schuyler Colfax</v>
+      </c>
+      <c r="G19" t="s">
+        <v>56</v>
+      </c>
+      <c r="H19" t="str">
+        <f t="shared" si="2"/>
+        <v>Schuyler Colfax</v>
+      </c>
+      <c r="I19" s="6">
         <v>115000</v>
       </c>
-      <c r="G19" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H19" s="1">
+      <c r="J19" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K19" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L19" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M19" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20" t="s">
-        <v>63</v>
+        <v>57</v>
+      </c>
+      <c r="C20" t="str">
+        <f t="shared" si="0"/>
+        <v>RUTHERFORD B. HAYES</v>
       </c>
       <c r="D20" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E20" t="s">
-        <v>64</v>
-      </c>
-      <c r="F20" s="4">
+        <v>55</v>
+      </c>
+      <c r="F20" t="str">
+        <f t="shared" si="1"/>
+        <v>William A. Wheeler</v>
+      </c>
+      <c r="G20" t="s">
+        <v>59</v>
+      </c>
+      <c r="H20" t="str">
+        <f t="shared" si="2"/>
+        <v>William A. Wheeler</v>
+      </c>
+      <c r="I20" s="6">
         <v>125000</v>
       </c>
-      <c r="G20" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H20" s="1">
+      <c r="J20" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K20" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L20" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M20" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" t="s">
-        <v>66</v>
+        <v>60</v>
+      </c>
+      <c r="C21" t="str">
+        <f t="shared" si="0"/>
+        <v>JAMES A. GARFIELD</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E21" t="s">
-        <v>67</v>
-      </c>
-      <c r="F21" s="4">
+        <v>55</v>
+      </c>
+      <c r="F21" t="str">
+        <f t="shared" si="1"/>
+        <v>Chester A. Arthur</v>
+      </c>
+      <c r="G21" t="s">
+        <v>62</v>
+      </c>
+      <c r="H21" t="str">
+        <f t="shared" si="2"/>
+        <v>Chester A. Arthur</v>
+      </c>
+      <c r="I21" s="6">
         <v>135000</v>
       </c>
-      <c r="G21" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H21" s="1">
+      <c r="J21" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K21" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L21" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M21" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
-      </c>
-      <c r="C22" t="s">
-        <v>68</v>
+        <v>62</v>
+      </c>
+      <c r="C22" t="str">
+        <f t="shared" si="0"/>
+        <v>CHESTER A. ARTHUR</v>
       </c>
       <c r="D22" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E22" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" s="4">
+        <v>55</v>
+      </c>
+      <c r="F22" t="str">
+        <f t="shared" si="1"/>
+        <v>Office vacant</v>
+      </c>
+      <c r="G22" t="s">
+        <v>35</v>
+      </c>
+      <c r="H22" t="str">
+        <f t="shared" si="2"/>
+        <v>Office vacant</v>
+      </c>
+      <c r="I22" s="6">
         <v>145000</v>
       </c>
-      <c r="G22" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H22" s="1">
+      <c r="J22" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K22" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L22" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M22" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" t="s">
-        <v>70</v>
+        <v>64</v>
+      </c>
+      <c r="C23" t="str">
+        <f t="shared" si="0"/>
+        <v>GROVER CLEVELAND</v>
       </c>
       <c r="D23" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="E23" t="s">
-        <v>71</v>
-      </c>
-      <c r="F23" s="4">
+        <v>24</v>
+      </c>
+      <c r="F23" t="str">
+        <f t="shared" si="1"/>
+        <v>Thomas A. Hendricks</v>
+      </c>
+      <c r="G23" t="s">
+        <v>66</v>
+      </c>
+      <c r="H23" t="str">
+        <f t="shared" si="2"/>
+        <v>Thomas A. Hendricks</v>
+      </c>
+      <c r="I23" s="6">
         <v>155000</v>
       </c>
-      <c r="G23" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H23" s="1">
+      <c r="J23" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K23" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L23" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M23" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
-      </c>
-      <c r="C24" t="s">
-        <v>73</v>
+        <v>67</v>
+      </c>
+      <c r="C24" t="str">
+        <f t="shared" si="0"/>
+        <v>BENJAMIN HARRISON</v>
       </c>
       <c r="D24" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E24" t="s">
-        <v>74</v>
-      </c>
-      <c r="F24" s="4">
+        <v>55</v>
+      </c>
+      <c r="F24" t="str">
+        <f t="shared" si="1"/>
+        <v>Levi P. Morton</v>
+      </c>
+      <c r="G24" t="s">
+        <v>69</v>
+      </c>
+      <c r="H24" t="str">
+        <f t="shared" si="2"/>
+        <v>Levi P. Morton</v>
+      </c>
+      <c r="I24" s="6">
         <v>165000</v>
       </c>
-      <c r="G24" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H24" s="1">
+      <c r="J24" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K24" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L24" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M24" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25" t="s">
-        <v>75</v>
+        <v>64</v>
+      </c>
+      <c r="C25" t="str">
+        <f t="shared" si="0"/>
+        <v>GROVER CLEVELAND</v>
       </c>
       <c r="D25" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="E25" t="s">
-        <v>76</v>
-      </c>
-      <c r="F25" s="4">
+        <v>24</v>
+      </c>
+      <c r="F25" t="str">
+        <f t="shared" si="1"/>
+        <v>Adlai Stevenson</v>
+      </c>
+      <c r="G25" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25" t="str">
+        <f t="shared" si="2"/>
+        <v>Adlai Stevenson</v>
+      </c>
+      <c r="I25" s="6">
         <v>175000</v>
       </c>
-      <c r="G25" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H25" s="1">
+      <c r="J25" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K25" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L25" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M25" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>77</v>
-      </c>
-      <c r="C26" t="s">
-        <v>78</v>
+        <v>72</v>
+      </c>
+      <c r="C26" t="str">
+        <f t="shared" si="0"/>
+        <v>WILLIAM MCKINLEY</v>
       </c>
       <c r="D26" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="E26" t="s">
-        <v>79</v>
-      </c>
-      <c r="F26" s="4">
+        <v>55</v>
+      </c>
+      <c r="F26" t="str">
+        <f t="shared" si="1"/>
+        <v>Garret Hobart</v>
+      </c>
+      <c r="G26" t="s">
+        <v>74</v>
+      </c>
+      <c r="H26" t="str">
+        <f t="shared" si="2"/>
+        <v>Garret Hobart</v>
+      </c>
+      <c r="I26" s="6">
         <v>185000</v>
       </c>
-      <c r="G26" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H26" s="1">
+      <c r="J26" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K26" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L26" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M26" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>80</v>
-      </c>
-      <c r="C27" t="s">
-        <v>81</v>
+        <v>75</v>
+      </c>
+      <c r="C27" t="str">
+        <f t="shared" si="0"/>
+        <v>THEODORE ROOSEVELT</v>
       </c>
       <c r="D27" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="E27" t="s">
-        <v>38</v>
-      </c>
-      <c r="F27" s="4">
+        <v>55</v>
+      </c>
+      <c r="F27" t="str">
+        <f t="shared" si="1"/>
+        <v>Office vacant</v>
+      </c>
+      <c r="G27" t="s">
+        <v>35</v>
+      </c>
+      <c r="H27" t="str">
+        <f t="shared" si="2"/>
+        <v>Office vacant</v>
+      </c>
+      <c r="I27" s="6">
         <v>195000</v>
       </c>
-      <c r="G27" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H27" s="1">
+      <c r="J27" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K27" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L27" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M27" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>82</v>
-      </c>
-      <c r="C28" t="s">
-        <v>83</v>
+        <v>77</v>
+      </c>
+      <c r="C28" t="str">
+        <f t="shared" si="0"/>
+        <v>WILLIAM HOWARD TAFT</v>
       </c>
       <c r="D28" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="E28" t="s">
-        <v>84</v>
-      </c>
-      <c r="F28" s="4">
+        <v>55</v>
+      </c>
+      <c r="F28" t="str">
+        <f t="shared" si="1"/>
+        <v>James S. Sherman</v>
+      </c>
+      <c r="G28" t="s">
+        <v>79</v>
+      </c>
+      <c r="H28" t="str">
+        <f t="shared" si="2"/>
+        <v>James S. Sherman</v>
+      </c>
+      <c r="I28" s="6">
         <v>205000</v>
       </c>
-      <c r="G28" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H28" s="1">
+      <c r="J28" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K28" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L28" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M28" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>85</v>
-      </c>
-      <c r="C29" t="s">
-        <v>86</v>
+        <v>80</v>
+      </c>
+      <c r="C29" t="str">
+        <f t="shared" si="0"/>
+        <v>WOODROW WILSON</v>
       </c>
       <c r="D29" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="E29" t="s">
-        <v>87</v>
-      </c>
-      <c r="F29" s="4">
+        <v>24</v>
+      </c>
+      <c r="F29" t="str">
+        <f t="shared" si="1"/>
+        <v>Thomas R. Marshall</v>
+      </c>
+      <c r="G29" t="s">
+        <v>82</v>
+      </c>
+      <c r="H29" t="str">
+        <f t="shared" si="2"/>
+        <v>Thomas R. Marshall</v>
+      </c>
+      <c r="I29" s="6">
         <v>225000</v>
       </c>
-      <c r="G29" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H29" s="1">
+      <c r="J29" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K29" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L29" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M29" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>85</v>
-      </c>
-      <c r="C30" t="s">
-        <v>86</v>
+        <v>80</v>
+      </c>
+      <c r="C30" t="str">
+        <f t="shared" si="0"/>
+        <v>WOODROW WILSON</v>
       </c>
       <c r="D30" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="E30" t="s">
-        <v>87</v>
-      </c>
-      <c r="F30" s="4">
+        <v>128</v>
+      </c>
+      <c r="F30" t="str">
+        <f t="shared" si="1"/>
+        <v>Thomas R. Marshall</v>
+      </c>
+      <c r="G30" t="s">
+        <v>82</v>
+      </c>
+      <c r="H30" t="str">
+        <f t="shared" si="2"/>
+        <v>Thomas R. Marshall</v>
+      </c>
+      <c r="I30" s="6">
         <v>225000</v>
       </c>
-      <c r="G30" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H30" s="1">
+      <c r="J30" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K30" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L30" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M30" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>88</v>
-      </c>
-      <c r="C31" t="s">
-        <v>89</v>
+        <v>83</v>
+      </c>
+      <c r="C31" t="str">
+        <f t="shared" si="0"/>
+        <v>WARREN G. HARDING</v>
       </c>
       <c r="D31" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="E31" t="s">
-        <v>90</v>
-      </c>
-      <c r="F31" s="4">
+        <v>55</v>
+      </c>
+      <c r="F31" t="str">
+        <f t="shared" si="1"/>
+        <v>Calvin Coolidge</v>
+      </c>
+      <c r="G31" t="s">
+        <v>85</v>
+      </c>
+      <c r="H31" t="str">
+        <f t="shared" si="2"/>
+        <v>Calvin Coolidge</v>
+      </c>
+      <c r="I31" s="6">
         <v>235000</v>
       </c>
-      <c r="G31" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H31" s="1">
+      <c r="J31" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K31" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L31" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M31" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>90</v>
-      </c>
-      <c r="C32" t="s">
-        <v>91</v>
+        <v>85</v>
+      </c>
+      <c r="C32" t="str">
+        <f t="shared" si="0"/>
+        <v>CALVIN COOLIDGE</v>
       </c>
       <c r="D32" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="E32" t="s">
-        <v>38</v>
-      </c>
-      <c r="F32" s="4">
+        <v>55</v>
+      </c>
+      <c r="F32" t="str">
+        <f t="shared" si="1"/>
+        <v>Office vacant</v>
+      </c>
+      <c r="G32" t="s">
+        <v>35</v>
+      </c>
+      <c r="H32" t="str">
+        <f t="shared" si="2"/>
+        <v>Office vacant</v>
+      </c>
+      <c r="I32" s="6">
         <v>245000</v>
       </c>
-      <c r="G32" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H32" s="1">
+      <c r="J32" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K32" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L32" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M32" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
-      </c>
-      <c r="C33" t="s">
-        <v>93</v>
+        <v>87</v>
+      </c>
+      <c r="C33" t="str">
+        <f t="shared" si="0"/>
+        <v>HERBERT HOOVER</v>
       </c>
       <c r="D33" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="E33" t="s">
-        <v>94</v>
-      </c>
-      <c r="F33" s="4">
+        <v>55</v>
+      </c>
+      <c r="F33" t="str">
+        <f t="shared" si="1"/>
+        <v>Charles Curtis</v>
+      </c>
+      <c r="G33" t="s">
+        <v>89</v>
+      </c>
+      <c r="H33" t="str">
+        <f t="shared" si="2"/>
+        <v>Charles Curtis</v>
+      </c>
+      <c r="I33" s="6">
         <v>255000</v>
       </c>
-      <c r="G33" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H33" s="1">
+      <c r="J33" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K33" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L33" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M33" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
-      </c>
-      <c r="C34" t="s">
-        <v>96</v>
+        <v>90</v>
+      </c>
+      <c r="C34" t="str">
+        <f t="shared" si="0"/>
+        <v>FRANKLIN D. ROOSEVELT</v>
       </c>
       <c r="D34" t="s">
-        <v>26</v>
+        <v>91</v>
       </c>
       <c r="E34" t="s">
-        <v>97</v>
-      </c>
-      <c r="F34" s="4">
+        <v>24</v>
+      </c>
+      <c r="F34" t="str">
+        <f t="shared" si="1"/>
+        <v>John Nance Garner</v>
+      </c>
+      <c r="G34" t="s">
+        <v>92</v>
+      </c>
+      <c r="H34" t="str">
+        <f t="shared" si="2"/>
+        <v>John Nance Garner</v>
+      </c>
+      <c r="I34" s="6">
         <v>265000</v>
       </c>
-      <c r="G34" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H34" s="1">
+      <c r="J34" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K34" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L34" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M34" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>98</v>
-      </c>
-      <c r="C35" t="s">
-        <v>99</v>
+        <v>93</v>
+      </c>
+      <c r="C35" t="str">
+        <f t="shared" si="0"/>
+        <v>HARRY S. TRUMAN</v>
       </c>
       <c r="D35" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="E35" t="s">
-        <v>38</v>
-      </c>
-      <c r="F35" s="4">
+        <v>24</v>
+      </c>
+      <c r="F35" t="str">
+        <f t="shared" si="1"/>
+        <v>Office vacant</v>
+      </c>
+      <c r="G35" t="s">
+        <v>35</v>
+      </c>
+      <c r="H35" t="str">
+        <f t="shared" si="2"/>
+        <v>Office vacant</v>
+      </c>
+      <c r="I35" s="6">
         <v>275000</v>
       </c>
-      <c r="G35" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H35" s="1">
+      <c r="J35" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K35" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L35" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M35" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>100</v>
-      </c>
-      <c r="C36" t="s">
-        <v>101</v>
+        <v>95</v>
+      </c>
+      <c r="C36" t="str">
+        <f t="shared" si="0"/>
+        <v>DWIGHT D. EISENHOWER</v>
       </c>
       <c r="D36" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="E36" t="s">
-        <v>102</v>
-      </c>
-      <c r="F36" s="4">
+        <v>55</v>
+      </c>
+      <c r="F36" t="str">
+        <f t="shared" si="1"/>
+        <v>Richard Nixon</v>
+      </c>
+      <c r="G36" t="s">
+        <v>97</v>
+      </c>
+      <c r="H36" t="str">
+        <f t="shared" si="2"/>
+        <v>Richard Nixon</v>
+      </c>
+      <c r="I36" s="6">
         <v>285000</v>
       </c>
-      <c r="G36" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H36" s="1">
+      <c r="J36" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K36" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L36" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M36" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>103</v>
-      </c>
-      <c r="C37" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="C37" t="str">
+        <f t="shared" si="0"/>
+        <v>JOHN F. KENNEDY</v>
       </c>
       <c r="D37" t="s">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="E37" t="s">
-        <v>105</v>
-      </c>
-      <c r="F37" s="4">
+        <v>24</v>
+      </c>
+      <c r="F37" t="str">
+        <f t="shared" si="1"/>
+        <v>Lyndon B. Johnson</v>
+      </c>
+      <c r="G37" t="s">
+        <v>100</v>
+      </c>
+      <c r="H37" t="str">
+        <f t="shared" si="2"/>
+        <v>Lyndon B. Johnson</v>
+      </c>
+      <c r="I37" s="6">
         <v>295000</v>
       </c>
-      <c r="G37" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H37" s="1">
+      <c r="J37" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K37" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L37" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M37" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>105</v>
-      </c>
-      <c r="C38" t="s">
-        <v>106</v>
+        <v>100</v>
+      </c>
+      <c r="C38" t="str">
+        <f t="shared" si="0"/>
+        <v>LYNDON B. JOHNSON</v>
       </c>
       <c r="D38" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="E38" t="s">
-        <v>38</v>
-      </c>
-      <c r="F38" s="4">
+        <v>24</v>
+      </c>
+      <c r="F38" t="str">
+        <f t="shared" si="1"/>
+        <v>Office vacant</v>
+      </c>
+      <c r="G38" t="s">
+        <v>35</v>
+      </c>
+      <c r="H38" t="str">
+        <f t="shared" si="2"/>
+        <v>Office vacant</v>
+      </c>
+      <c r="I38" s="6">
         <v>305000</v>
       </c>
-      <c r="G38" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H38" s="1">
+      <c r="J38" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K38" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L38" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M38" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>37</v>
       </c>
       <c r="B39" t="s">
+        <v>97</v>
+      </c>
+      <c r="C39" t="str">
+        <f t="shared" si="0"/>
+        <v>RICHARD NIXON</v>
+      </c>
+      <c r="D39" t="s">
         <v>102</v>
       </c>
-      <c r="C39" t="s">
-        <v>107</v>
-      </c>
-      <c r="D39" t="s">
-        <v>60</v>
-      </c>
       <c r="E39" t="s">
-        <v>108</v>
-      </c>
-      <c r="F39" s="4">
+        <v>55</v>
+      </c>
+      <c r="F39" t="str">
+        <f t="shared" si="1"/>
+        <v>Spiro Agnew</v>
+      </c>
+      <c r="G39" t="s">
+        <v>103</v>
+      </c>
+      <c r="H39" t="str">
+        <f t="shared" si="2"/>
+        <v>Spiro Agnew</v>
+      </c>
+      <c r="I39" s="6">
         <v>315000</v>
       </c>
-      <c r="G39" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H39" s="1">
+      <c r="J39" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K39" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L39" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M39" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>109</v>
-      </c>
-      <c r="C40" t="s">
-        <v>110</v>
+        <v>104</v>
+      </c>
+      <c r="C40" t="str">
+        <f t="shared" si="0"/>
+        <v>GERALD FORD</v>
       </c>
       <c r="D40" t="s">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c r="E40" t="s">
-        <v>38</v>
-      </c>
-      <c r="F40" s="4">
+        <v>55</v>
+      </c>
+      <c r="F40" t="str">
+        <f t="shared" si="1"/>
+        <v>Office vacant</v>
+      </c>
+      <c r="G40" t="s">
+        <v>35</v>
+      </c>
+      <c r="H40" t="str">
+        <f t="shared" si="2"/>
+        <v>Office vacant</v>
+      </c>
+      <c r="I40" s="6">
         <v>325000</v>
       </c>
-      <c r="G40" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H40" s="1">
+      <c r="J40" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K40" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L40" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M40" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>111</v>
-      </c>
-      <c r="C41" t="s">
-        <v>112</v>
+        <v>106</v>
+      </c>
+      <c r="C41" t="str">
+        <f t="shared" si="0"/>
+        <v>JIMMY CARTER</v>
       </c>
       <c r="D41" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="E41" t="s">
-        <v>113</v>
-      </c>
-      <c r="F41" s="4">
+        <v>24</v>
+      </c>
+      <c r="F41" t="str">
+        <f t="shared" si="1"/>
+        <v>Walter Mondale</v>
+      </c>
+      <c r="G41" t="s">
+        <v>108</v>
+      </c>
+      <c r="H41" t="str">
+        <f t="shared" si="2"/>
+        <v>Walter Mondale</v>
+      </c>
+      <c r="I41" s="6">
         <v>335000</v>
       </c>
-      <c r="G41" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H41" s="1">
+      <c r="J41" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K41" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L41" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M41" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>114</v>
-      </c>
-      <c r="C42" t="s">
-        <v>115</v>
+        <v>109</v>
+      </c>
+      <c r="C42" t="str">
+        <f t="shared" si="0"/>
+        <v>RONALD REAGAN</v>
       </c>
       <c r="D42" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="E42" t="s">
-        <v>116</v>
-      </c>
-      <c r="F42" s="4">
+        <v>55</v>
+      </c>
+      <c r="F42" t="str">
+        <f t="shared" si="1"/>
+        <v>George H. W. Bush</v>
+      </c>
+      <c r="G42" t="s">
+        <v>111</v>
+      </c>
+      <c r="H42" t="str">
+        <f t="shared" si="2"/>
+        <v>George H. W. Bush</v>
+      </c>
+      <c r="I42" s="6">
         <v>345000</v>
       </c>
-      <c r="G42" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H42" s="1">
+      <c r="J42" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K42" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L42" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M42" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>116</v>
-      </c>
-      <c r="C43" t="s">
-        <v>117</v>
+        <v>111</v>
+      </c>
+      <c r="C43" t="str">
+        <f t="shared" si="0"/>
+        <v>GEORGE H. W. BUSH</v>
       </c>
       <c r="D43" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="E43" t="s">
-        <v>118</v>
-      </c>
-      <c r="F43" s="4">
+        <v>55</v>
+      </c>
+      <c r="F43" t="str">
+        <f t="shared" si="1"/>
+        <v>Dan Quayle</v>
+      </c>
+      <c r="G43" t="s">
+        <v>113</v>
+      </c>
+      <c r="H43" t="str">
+        <f t="shared" si="2"/>
+        <v>Dan Quayle</v>
+      </c>
+      <c r="I43" s="6">
         <v>355000</v>
       </c>
-      <c r="G43" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H43" s="1">
+      <c r="J43" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K43" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L43" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M43" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>119</v>
-      </c>
-      <c r="C44" t="s">
-        <v>120</v>
+        <v>114</v>
+      </c>
+      <c r="C44" t="str">
+        <f t="shared" si="0"/>
+        <v>BILL CLINTON</v>
       </c>
       <c r="D44" t="s">
-        <v>26</v>
+        <v>115</v>
       </c>
       <c r="E44" t="s">
-        <v>121</v>
-      </c>
-      <c r="F44" s="4">
+        <v>24</v>
+      </c>
+      <c r="F44" t="str">
+        <f t="shared" si="1"/>
+        <v>Al Gore</v>
+      </c>
+      <c r="G44" t="s">
+        <v>116</v>
+      </c>
+      <c r="H44" t="str">
+        <f t="shared" si="2"/>
+        <v>Al Gore</v>
+      </c>
+      <c r="I44" s="6">
         <v>365000</v>
       </c>
-      <c r="G44" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H44" s="1">
+      <c r="J44" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K44" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L44" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M44" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>122</v>
-      </c>
-      <c r="C45" t="s">
-        <v>123</v>
+        <v>117</v>
+      </c>
+      <c r="C45" t="str">
+        <f t="shared" si="0"/>
+        <v>GEORGE W. BUSH</v>
       </c>
       <c r="D45" t="s">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="E45" t="s">
-        <v>124</v>
-      </c>
-      <c r="F45" s="4">
+        <v>55</v>
+      </c>
+      <c r="F45" t="str">
+        <f t="shared" si="1"/>
+        <v>Dick Cheney</v>
+      </c>
+      <c r="G45" t="s">
+        <v>119</v>
+      </c>
+      <c r="H45" t="str">
+        <f t="shared" si="2"/>
+        <v>Dick Cheney</v>
+      </c>
+      <c r="I45" s="6">
         <v>375000</v>
       </c>
-      <c r="G45" s="1">
-        <v>44391</v>
-      </c>
-      <c r="H45" s="1">
+      <c r="J45" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K45" s="1">
         <v>40972</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="L45" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M45" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>44</v>
       </c>
       <c r="B46" t="s">
+        <v>120</v>
+      </c>
+      <c r="C46" t="str">
+        <f t="shared" si="0"/>
+        <v>BARACK OBAMA</v>
+      </c>
+      <c r="D46" t="s">
+        <v>121</v>
+      </c>
+      <c r="E46" t="s">
+        <v>24</v>
+      </c>
+      <c r="F46" t="str">
+        <f t="shared" si="1"/>
+        <v>Joe Biden</v>
+      </c>
+      <c r="G46" t="s">
+        <v>122</v>
+      </c>
+      <c r="H46" t="str">
+        <f t="shared" si="2"/>
+        <v>Joe Biden</v>
+      </c>
+      <c r="I46" s="6">
+        <v>395000</v>
+      </c>
+      <c r="J46" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K46" s="1">
+        <v>43862</v>
+      </c>
+      <c r="L46" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M46" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47" t="s">
+        <v>123</v>
+      </c>
+      <c r="C47" t="str">
+        <f t="shared" si="0"/>
+        <v>DONALD TRUMP</v>
+      </c>
+      <c r="D47" t="s">
+        <v>124</v>
+      </c>
+      <c r="E47" t="s">
+        <v>55</v>
+      </c>
+      <c r="F47" t="str">
+        <f t="shared" si="1"/>
+        <v>Mike Pence</v>
+      </c>
+      <c r="G47" t="s">
         <v>125</v>
       </c>
-      <c r="C46" t="s">
-        <v>126</v>
-      </c>
-      <c r="D46" t="s">
-        <v>26</v>
-      </c>
-      <c r="E46" t="s">
-        <v>127</v>
-      </c>
-      <c r="F46" s="4">
-        <v>395000</v>
-      </c>
-      <c r="G46" s="2">
-        <v>44391</v>
-      </c>
-      <c r="H46" s="2">
+      <c r="H47" t="str">
+        <f t="shared" si="2"/>
+        <v>Mike Pence</v>
+      </c>
+      <c r="I47" s="6">
+        <v>405000</v>
+      </c>
+      <c r="J47" s="1">
+        <v>44391</v>
+      </c>
+      <c r="K47" s="1">
         <v>43862</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47">
-        <v>44</v>
-      </c>
-      <c r="B47" t="s">
-        <v>125</v>
-      </c>
-      <c r="C47" t="s">
-        <v>126</v>
-      </c>
-      <c r="D47" t="s">
-        <v>26</v>
-      </c>
-      <c r="E47" t="s">
-        <v>127</v>
-      </c>
-      <c r="F47" s="4">
-        <v>395000</v>
-      </c>
-      <c r="G47" s="2">
-        <v>44391</v>
-      </c>
-      <c r="H47" s="2">
-        <v>43862</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48">
-        <v>45</v>
-      </c>
-      <c r="B48" t="s">
-        <v>128</v>
-      </c>
-      <c r="C48" t="s">
-        <v>129</v>
-      </c>
-      <c r="D48" t="s">
-        <v>132</v>
-      </c>
-      <c r="E48" t="s">
-        <v>130</v>
-      </c>
-      <c r="F48" s="4">
-        <v>405000</v>
-      </c>
-      <c r="G48" s="2">
-        <v>44391</v>
-      </c>
-      <c r="H48" s="2">
-        <v>43862</v>
+      <c r="L47" t="str">
+        <f t="shared" si="3"/>
+        <v>14-07-2021</v>
+      </c>
+      <c r="M47" t="str">
+        <f t="shared" si="4"/>
+        <v>14/07/2021</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F48" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L48" t="str">
+        <f t="shared" si="3"/>
+        <v>00-01-1900</v>
+      </c>
+      <c r="M48" t="str">
+        <f t="shared" si="4"/>
+        <v>00/01/1900</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:L48" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <dataConsolidate/>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
